--- a/artfynd/A 37564-2026 artfynd.xlsx
+++ b/artfynd/A 37564-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373296</v>
       </c>
       <c r="B2" t="n">
-        <v>79675</v>
+        <v>79680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137373297</v>
       </c>
       <c r="B3" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37564-2026 artfynd.xlsx
+++ b/artfynd/A 37564-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373296</v>
       </c>
       <c r="B2" t="n">
-        <v>79680</v>
+        <v>79691</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37564-2026 artfynd.xlsx
+++ b/artfynd/A 37564-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373296</v>
       </c>
       <c r="B2" t="n">
-        <v>79691</v>
+        <v>79692</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37564-2026 artfynd.xlsx
+++ b/artfynd/A 37564-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373296</v>
       </c>
       <c r="B2" t="n">
-        <v>79692</v>
+        <v>79694</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37564-2026 artfynd.xlsx
+++ b/artfynd/A 37564-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373296</v>
       </c>
       <c r="B2" t="n">
-        <v>79694</v>
+        <v>79698</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137373297</v>
       </c>
       <c r="B3" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
